--- a/Excel/MonsterLegacyConfig.xlsx
+++ b/Excel/MonsterLegacyConfig.xlsx
@@ -1349,10 +1349,10 @@
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="11">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R6" s="11">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:18">
@@ -1397,10 +1397,10 @@
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="11">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R7" s="11">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:18">
@@ -1445,10 +1445,10 @@
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R8" s="11">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:18">

--- a/Excel/MonsterLegacyConfig.xlsx
+++ b/Excel/MonsterLegacyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -83,21 +83,18 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Attr</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>int[]</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
     <t>传世圣战</t>
   </si>
   <si>
@@ -107,7 +104,13 @@
     <t>30000</t>
   </si>
   <si>
+    <t>1.2</t>
+  </si>
+  <si>
     <t>3000000</t>
+  </si>
+  <si>
+    <t>1.6</t>
   </si>
   <si>
     <t>传世法神</t>
@@ -123,12 +126,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -750,35 +752,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1100,486 +1087,452 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R36"/>
+  <dimension ref="C1:R36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="1" customWidth="1"/>
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.91666666666667" style="1" customWidth="1"/>
     <col min="6" max="7" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.0833333333333" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15" style="3" customWidth="1"/>
-    <col min="11" max="11" width="15.5833333333333" style="3" customWidth="1"/>
-    <col min="12" max="13" width="12.8333333333333" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.0833333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15.5833333333333" style="2" customWidth="1"/>
+    <col min="12" max="13" width="12.8333333333333" style="2" customWidth="1"/>
     <col min="14" max="14" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.0833333333333" style="4" customWidth="1"/>
-    <col min="16" max="16" width="13.3333333333333" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.58333333333333" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="2"/>
+    <col min="15" max="15" width="13.0833333333333" style="2" customWidth="1"/>
+    <col min="16" max="16" width="13.3333333333333" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.58333333333333" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.91666666666667" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="6" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1"/>
+    <row r="2" s="1" customFormat="1" customHeight="1"/>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="6" t="s">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="R4" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="J5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="M5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="N5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="R5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:18">
+    </row>
+    <row r="6" customHeight="1" spans="3:18">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <v>10</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="9">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9">
-        <v>1</v>
-      </c>
-      <c r="G6" s="9">
-        <v>10</v>
-      </c>
-      <c r="H6" s="13" t="s">
+      <c r="I6" s="5">
+        <v>2</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="13" t="s">
+      <c r="K6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N6" s="9">
+      <c r="M6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="4">
         <v>100</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="4">
         <v>3</v>
       </c>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="11">
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4">
         <v>100</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:18">
+    <row r="7" customHeight="1" spans="3:18">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="4">
         <v>1</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="4">
         <v>10</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N7" s="9">
+      <c r="M7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="4">
         <v>100</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="4">
         <v>3</v>
       </c>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="11">
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4">
         <v>100</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:18">
+    <row r="8" customHeight="1" spans="3:18">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="4">
         <v>1</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="4">
         <v>10</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="13" t="s">
+      <c r="K8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="N8" s="9">
+      <c r="L8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="4">
         <v>100</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="4">
         <v>3</v>
       </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11">
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4">
         <v>100</v>
       </c>
-      <c r="R8" s="11">
+      <c r="R8" s="4">
         <v>50</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:18">
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-    </row>
-    <row r="10" customHeight="1" spans="1:18">
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-    </row>
-    <row r="11" customHeight="1" spans="1:18">
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:18">
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:18">
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:18">
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:18">
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
+    <row r="9" customHeight="1" spans="3:18">
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+    </row>
+    <row r="10" customHeight="1" spans="3:18">
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+    </row>
+    <row r="11" customHeight="1" spans="3:18">
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:18">
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+    </row>
+    <row r="13" customHeight="1" spans="3:18">
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:18">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:18">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
     </row>
     <row r="23" customHeight="1" spans="8:11">
-      <c r="H23" s="10"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" customHeight="1" spans="8:11">
-      <c r="H24" s="10"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="27" customHeight="1" spans="8:11">
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" customHeight="1" spans="8:11">
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" customHeight="1" spans="8:11">
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
     </row>
     <row r="30" customHeight="1" spans="8:11">
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
     </row>
     <row r="31" customHeight="1" spans="8:11">
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
     </row>
     <row r="32" customHeight="1" spans="8:11">
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
     </row>
     <row r="33" customHeight="1" spans="10:11">
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" customHeight="1" spans="10:11">
-      <c r="J34" s="10"/>
-      <c r="K34" s="10"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
     </row>
     <row r="35" customHeight="1" spans="10:11">
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
     </row>
     <row r="36" customHeight="1" spans="10:11">
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/MonsterLegacyConfig.xlsx
+++ b/Excel/MonsterLegacyConfig.xlsx
@@ -104,13 +104,13 @@
     <t>30000</t>
   </si>
   <si>
-    <t>1.2</t>
+    <t>1.5</t>
   </si>
   <si>
     <t>3000000</t>
   </si>
   <si>
-    <t>1.6</t>
+    <t>1.8</t>
   </si>
   <si>
     <t>传世法神</t>
